--- a/web_crawl/電動車_退稅進度.xlsx
+++ b/web_crawl/電動車_退稅進度.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" state="visible" r:id="rId1"/>
